--- a/chapters/04/python_analytics/AIHE-PY23_agent_based_simulation_of_clinician_adoption/data/xlsx/23_agent_based_clinician_adoption_template.xlsx
+++ b/chapters/04/python_analytics/AIHE-PY23_agent_based_simulation_of_clinician_adoption/data/xlsx/23_agent_based_clinician_adoption_template.xlsx
@@ -82,7 +82,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -90,7 +90,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,10 +120,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,10 +131,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -449,7 +449,7 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>Clinician behavior, professional networks, technology acceptance, peer effects, implementation heterogeneity, and adaptive governance.</t>
+          <t>Clinician behaviour, professional networks, technology acceptance, peer effects, implementation heterogeneity, and adaptive governance.</t>
         </is>
       </c>
     </row>
